--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9478,6 +9478,42 @@
       <c r="J251" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="C252" t="n">
+        <v>399.73</v>
+      </c>
+      <c r="D252" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="E252" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="F252" t="n">
+        <v>378.37</v>
+      </c>
+      <c r="G252" t="n">
+        <v>372.89</v>
+      </c>
+      <c r="H252" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="I252" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12135,6 +12171,16 @@
       </c>
       <c r="B264" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -12303,28 +12349,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1053275001755937</v>
+        <v>-0.1076571064606818</v>
       </c>
       <c r="J2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02412012559964183</v>
+        <v>0.02533555406034671</v>
       </c>
       <c r="M2" t="n">
-        <v>4.021522399669801</v>
+        <v>4.016963225784576</v>
       </c>
       <c r="N2" t="n">
-        <v>28.86294697525672</v>
+        <v>28.79080747608491</v>
       </c>
       <c r="O2" t="n">
-        <v>5.372424683069714</v>
+        <v>5.365706614797804</v>
       </c>
       <c r="P2" t="n">
-        <v>391.9982567753223</v>
+        <v>392.0211118872793</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12385,28 +12431,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1124892360691016</v>
+        <v>-0.1176203751232249</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01836606647904915</v>
+        <v>0.02011148983046473</v>
       </c>
       <c r="M3" t="n">
-        <v>4.989087979613696</v>
+        <v>4.993658311110953</v>
       </c>
       <c r="N3" t="n">
-        <v>43.49062679986606</v>
+        <v>43.52524893308</v>
       </c>
       <c r="O3" t="n">
-        <v>6.594742360385738</v>
+        <v>6.597366818138886</v>
       </c>
       <c r="P3" t="n">
-        <v>410.0260351229141</v>
+        <v>410.0763752848117</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12467,28 +12513,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4492525144093388</v>
+        <v>-0.4531193586277577</v>
       </c>
       <c r="J4" t="n">
+        <v>251</v>
+      </c>
+      <c r="K4" t="n">
         <v>250</v>
       </c>
-      <c r="K4" t="n">
-        <v>249</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1889715255154345</v>
+        <v>0.1925540174155942</v>
       </c>
       <c r="M4" t="n">
-        <v>5.971877394894471</v>
+        <v>5.96850010534928</v>
       </c>
       <c r="N4" t="n">
-        <v>55.84661451072679</v>
+        <v>55.74105315628075</v>
       </c>
       <c r="O4" t="n">
-        <v>7.473059247104012</v>
+        <v>7.465993112525671</v>
       </c>
       <c r="P4" t="n">
-        <v>412.9505984420954</v>
+        <v>412.988440726511</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12549,28 +12595,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.159192861565016</v>
+        <v>-1.1576793535004</v>
       </c>
       <c r="J5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5645255056647287</v>
+        <v>0.5658179364919411</v>
       </c>
       <c r="M5" t="n">
-        <v>6.362047526241319</v>
+        <v>6.346718769287215</v>
       </c>
       <c r="N5" t="n">
-        <v>66.65471446673614</v>
+        <v>66.40724534497546</v>
       </c>
       <c r="O5" t="n">
-        <v>8.164233856690789</v>
+        <v>8.149064077854307</v>
       </c>
       <c r="P5" t="n">
-        <v>418.3618546393512</v>
+        <v>418.3470060374711</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12631,28 +12677,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.403060644714389</v>
+        <v>-1.400320790289963</v>
       </c>
       <c r="J6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6317506312184247</v>
+        <v>0.6325479905138217</v>
       </c>
       <c r="M6" t="n">
-        <v>6.638499094961762</v>
+        <v>6.630752400017196</v>
       </c>
       <c r="N6" t="n">
-        <v>73.78864472978813</v>
+        <v>73.55394007044316</v>
       </c>
       <c r="O6" t="n">
-        <v>8.590031707146844</v>
+        <v>8.57635937157738</v>
       </c>
       <c r="P6" t="n">
-        <v>412.2241191040418</v>
+        <v>412.1972391629904</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12709,28 +12755,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.185169023301845</v>
+        <v>-1.183395555830341</v>
       </c>
       <c r="J7" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K7" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5749763908528448</v>
+        <v>0.5761431524617417</v>
       </c>
       <c r="M7" t="n">
-        <v>6.304666283818319</v>
+        <v>6.291979400296744</v>
       </c>
       <c r="N7" t="n">
-        <v>66.76732045230881</v>
+        <v>66.5261497103581</v>
       </c>
       <c r="O7" t="n">
-        <v>8.17112724489766</v>
+        <v>8.156356399174701</v>
       </c>
       <c r="P7" t="n">
-        <v>402.2580416787299</v>
+        <v>402.240642688234</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12787,28 +12833,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9808142700878799</v>
+        <v>-0.9818273428033401</v>
       </c>
       <c r="J8" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K8" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4528204996530575</v>
+        <v>0.4553242836865627</v>
       </c>
       <c r="M8" t="n">
-        <v>6.489030308488862</v>
+        <v>6.467113473550993</v>
       </c>
       <c r="N8" t="n">
-        <v>74.75110411869687</v>
+        <v>74.46139478881859</v>
       </c>
       <c r="O8" t="n">
-        <v>8.64587208549241</v>
+        <v>8.629101621189694</v>
       </c>
       <c r="P8" t="n">
-        <v>409.2497865284867</v>
+        <v>409.259725499926</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12865,28 +12911,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5634012471698356</v>
+        <v>-0.5636161983978222</v>
       </c>
       <c r="J9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2532160226000711</v>
+        <v>0.254902936487829</v>
       </c>
       <c r="M9" t="n">
-        <v>5.969244601032588</v>
+        <v>5.946578719412092</v>
       </c>
       <c r="N9" t="n">
-        <v>60.19767775312402</v>
+        <v>59.95821119648841</v>
       </c>
       <c r="O9" t="n">
-        <v>7.75871624388494</v>
+        <v>7.743268766902542</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6663879216771</v>
+        <v>402.6684967477102</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12924,7 +12970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25975,6 +26021,58 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>-35.171619196003334,173.09537693729013</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>-35.17195319277691,173.09617619485604</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-35.172366279208525,173.0968660567809</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-35.17270593467821,173.09762041785729</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-35.17302728505254,173.09838034319256</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-35.17309812587352,173.0992503256003</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-35.173034610135915,173.1001266499972</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-35.17284594483807,173.10097534383422</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9514,6 +9514,42 @@
       <c r="J252" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="C253" t="n">
+        <v>403.59</v>
+      </c>
+      <c r="D253" t="n">
+        <v>398.14</v>
+      </c>
+      <c r="E253" t="n">
+        <v>393.27</v>
+      </c>
+      <c r="F253" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="G253" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="H253" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="I253" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12181,6 +12217,16 @@
       </c>
       <c r="B265" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -12349,28 +12395,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1076571064606818</v>
+        <v>-0.1093477434047235</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02533555406034671</v>
+        <v>0.02630497312675595</v>
       </c>
       <c r="M2" t="n">
-        <v>4.016963225784576</v>
+        <v>4.009214637783995</v>
       </c>
       <c r="N2" t="n">
-        <v>28.79080747608491</v>
+        <v>28.69915546481202</v>
       </c>
       <c r="O2" t="n">
-        <v>5.365706614797804</v>
+        <v>5.357159271928736</v>
       </c>
       <c r="P2" t="n">
-        <v>392.0211118872793</v>
+        <v>392.0377886877809</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12431,28 +12477,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1176203751232249</v>
+        <v>-0.119953161992594</v>
       </c>
       <c r="J3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02011148983046473</v>
+        <v>0.02104767328567803</v>
       </c>
       <c r="M3" t="n">
-        <v>4.993658311110953</v>
+        <v>4.985111356020348</v>
       </c>
       <c r="N3" t="n">
-        <v>43.52524893308</v>
+        <v>43.39555307056576</v>
       </c>
       <c r="O3" t="n">
-        <v>6.597366818138886</v>
+        <v>6.587530119139172</v>
       </c>
       <c r="P3" t="n">
-        <v>410.0763752848117</v>
+        <v>410.0993863880353</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12513,28 +12559,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4531193586277577</v>
+        <v>-0.4549622435946236</v>
       </c>
       <c r="J4" t="n">
+        <v>252</v>
+      </c>
+      <c r="K4" t="n">
         <v>251</v>
       </c>
-      <c r="K4" t="n">
-        <v>250</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1925540174155942</v>
+        <v>0.1950288966658084</v>
       </c>
       <c r="M4" t="n">
-        <v>5.96850010534928</v>
+        <v>5.954351187976206</v>
       </c>
       <c r="N4" t="n">
-        <v>55.74105315628075</v>
+        <v>55.54577627985159</v>
       </c>
       <c r="O4" t="n">
-        <v>7.465993112525671</v>
+        <v>7.452903882370387</v>
       </c>
       <c r="P4" t="n">
-        <v>412.988440726511</v>
+        <v>413.0065743614828</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12595,28 +12641,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1576793535004</v>
+        <v>-1.15331922731312</v>
       </c>
       <c r="J5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5658179364919411</v>
+        <v>0.5654130076411604</v>
       </c>
       <c r="M5" t="n">
-        <v>6.346718769287215</v>
+        <v>6.350124798530852</v>
       </c>
       <c r="N5" t="n">
-        <v>66.40724534497546</v>
+        <v>66.29402229143926</v>
       </c>
       <c r="O5" t="n">
-        <v>8.149064077854307</v>
+        <v>8.142114116827353</v>
       </c>
       <c r="P5" t="n">
-        <v>418.3470060374711</v>
+        <v>418.3039968302945</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12677,28 +12723,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.400320790289963</v>
+        <v>-1.395844165852904</v>
       </c>
       <c r="J6" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K6" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6325479905138217</v>
+        <v>0.6324559759523697</v>
       </c>
       <c r="M6" t="n">
-        <v>6.630752400017196</v>
+        <v>6.635045556671524</v>
       </c>
       <c r="N6" t="n">
-        <v>73.55394007044316</v>
+        <v>73.42049602999236</v>
       </c>
       <c r="O6" t="n">
-        <v>8.57635937157738</v>
+        <v>8.568576079489075</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1972391629904</v>
+        <v>412.1530807924305</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12755,28 +12801,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.183395555830341</v>
+        <v>-1.180266138434447</v>
       </c>
       <c r="J7" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K7" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5761431524617417</v>
+        <v>0.576559389011319</v>
       </c>
       <c r="M7" t="n">
-        <v>6.291979400296744</v>
+        <v>6.289096176006127</v>
       </c>
       <c r="N7" t="n">
-        <v>66.5261497103581</v>
+        <v>66.33958208232099</v>
       </c>
       <c r="O7" t="n">
-        <v>8.156356399174701</v>
+        <v>8.144911422619707</v>
       </c>
       <c r="P7" t="n">
-        <v>402.240642688234</v>
+        <v>402.2097734529548</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12833,28 +12879,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9818273428033401</v>
+        <v>-0.9821372207568849</v>
       </c>
       <c r="J8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4553242836865627</v>
+        <v>0.457504896898097</v>
       </c>
       <c r="M8" t="n">
-        <v>6.467113473550993</v>
+        <v>6.442632873948686</v>
       </c>
       <c r="N8" t="n">
-        <v>74.46139478881859</v>
+        <v>74.16667222772473</v>
       </c>
       <c r="O8" t="n">
-        <v>8.629101621189694</v>
+        <v>8.612007444709086</v>
       </c>
       <c r="P8" t="n">
-        <v>409.259725499926</v>
+        <v>409.2627822016202</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12911,28 +12957,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5636161983978222</v>
+        <v>-0.5635157730802396</v>
       </c>
       <c r="J9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L9" t="n">
-        <v>0.254902936487829</v>
+        <v>0.2563892281837522</v>
       </c>
       <c r="M9" t="n">
-        <v>5.946578719412092</v>
+        <v>5.923585171846223</v>
       </c>
       <c r="N9" t="n">
-        <v>59.95821119648841</v>
+        <v>59.72036152047747</v>
       </c>
       <c r="O9" t="n">
-        <v>7.743268766902542</v>
+        <v>7.727895025197836</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6684967477102</v>
+        <v>402.6675061311307</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12970,7 +13016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26073,6 +26119,58 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-35.17161313708936,173.09538247307506</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-35.17192466821538,173.09620048596594</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-35.172344696079975,173.09688047507018</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-35.17267295652387,173.09763651305857</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-35.17300626774387,173.0983850568473</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-35.17308153919203,173.09925081765476</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-35.17302679566752,173.10012580869002</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-35.17284258193288,173.10097454340635</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J253"/>
+  <dimension ref="A1:J254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9548,6 +9548,42 @@
         <v>387.59</v>
       </c>
       <c r="J253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>387.87</v>
+      </c>
+      <c r="C254" t="n">
+        <v>405.02</v>
+      </c>
+      <c r="D254" t="n">
+        <v>401.19</v>
+      </c>
+      <c r="E254" t="n">
+        <v>394.9</v>
+      </c>
+      <c r="F254" t="n">
+        <v>382.18</v>
+      </c>
+      <c r="G254" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="H254" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="I254" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="J254" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9564,7 +9600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12227,6 +12263,16 @@
       </c>
       <c r="B266" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -12395,28 +12441,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1093477434047235</v>
+        <v>-0.1101944966554576</v>
       </c>
       <c r="J2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02630497312675595</v>
+        <v>0.02690907918381003</v>
       </c>
       <c r="M2" t="n">
-        <v>4.009214637783995</v>
+        <v>3.997435805575283</v>
       </c>
       <c r="N2" t="n">
-        <v>28.69915546481202</v>
+        <v>28.59146069792886</v>
       </c>
       <c r="O2" t="n">
-        <v>5.357159271928736</v>
+        <v>5.347098343768222</v>
       </c>
       <c r="P2" t="n">
-        <v>392.0377886877809</v>
+        <v>392.0461593377261</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12477,28 +12523,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.119953161992594</v>
+        <v>-0.1212327225825532</v>
       </c>
       <c r="J3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02104767328567803</v>
+        <v>0.02165395448766894</v>
       </c>
       <c r="M3" t="n">
-        <v>4.985111356020348</v>
+        <v>4.971814161069883</v>
       </c>
       <c r="N3" t="n">
-        <v>43.39555307056576</v>
+        <v>43.23713808424776</v>
       </c>
       <c r="O3" t="n">
-        <v>6.587530119139172</v>
+        <v>6.575495272924144</v>
       </c>
       <c r="P3" t="n">
-        <v>410.0993863880353</v>
+        <v>410.1120355910624</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12559,28 +12605,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4549622435946236</v>
+        <v>-0.4546154528766961</v>
       </c>
       <c r="J4" t="n">
+        <v>253</v>
+      </c>
+      <c r="K4" t="n">
         <v>252</v>
       </c>
-      <c r="K4" t="n">
-        <v>251</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1950288966658084</v>
+        <v>0.196066085627962</v>
       </c>
       <c r="M4" t="n">
-        <v>5.954351187976206</v>
+        <v>5.932808152198958</v>
       </c>
       <c r="N4" t="n">
-        <v>55.54577627985159</v>
+        <v>55.3263176871102</v>
       </c>
       <c r="O4" t="n">
-        <v>7.452903882370387</v>
+        <v>7.438166285255406</v>
       </c>
       <c r="P4" t="n">
-        <v>413.0065743614828</v>
+        <v>413.0031545996738</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12641,28 +12687,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.15331922731312</v>
+        <v>-1.147879118649777</v>
       </c>
       <c r="J5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5654130076411604</v>
+        <v>0.5641990720344543</v>
       </c>
       <c r="M5" t="n">
-        <v>6.350124798530852</v>
+        <v>6.360435629844138</v>
       </c>
       <c r="N5" t="n">
-        <v>66.29402229143926</v>
+        <v>66.26894290875622</v>
       </c>
       <c r="O5" t="n">
-        <v>8.142114116827353</v>
+        <v>8.140573868515427</v>
       </c>
       <c r="P5" t="n">
-        <v>418.3039968302945</v>
+        <v>418.2502181819748</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12723,28 +12769,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.395844165852904</v>
+        <v>-1.390409324918653</v>
       </c>
       <c r="J6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6324559759523697</v>
+        <v>0.6317742543877234</v>
       </c>
       <c r="M6" t="n">
-        <v>6.635045556671524</v>
+        <v>6.646473454142138</v>
       </c>
       <c r="N6" t="n">
-        <v>73.42049602999236</v>
+        <v>73.366790100958</v>
       </c>
       <c r="O6" t="n">
-        <v>8.568576079489075</v>
+        <v>8.565441617392416</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1530807924305</v>
+        <v>412.0993542186865</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12801,28 +12847,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.180266138434447</v>
+        <v>-1.177650573175303</v>
       </c>
       <c r="J7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L7" t="n">
-        <v>0.576559389011319</v>
+        <v>0.5772510744522956</v>
       </c>
       <c r="M7" t="n">
-        <v>6.289096176006127</v>
+        <v>6.282659695425917</v>
       </c>
       <c r="N7" t="n">
-        <v>66.33958208232099</v>
+        <v>66.13214460949138</v>
       </c>
       <c r="O7" t="n">
-        <v>8.144911422619707</v>
+        <v>8.132167276285664</v>
       </c>
       <c r="P7" t="n">
-        <v>402.2097734529548</v>
+        <v>402.183917064244</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12879,28 +12925,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9821372207568849</v>
+        <v>-0.9833915321226121</v>
       </c>
       <c r="J8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L8" t="n">
-        <v>0.457504896898097</v>
+        <v>0.4601074989024228</v>
       </c>
       <c r="M8" t="n">
-        <v>6.442632873948686</v>
+        <v>6.421908975261571</v>
       </c>
       <c r="N8" t="n">
-        <v>74.16667222772473</v>
+        <v>73.88612001855375</v>
       </c>
       <c r="O8" t="n">
-        <v>8.612007444709086</v>
+        <v>8.595703579030268</v>
       </c>
       <c r="P8" t="n">
-        <v>409.2627822016202</v>
+        <v>409.2751818013332</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12957,28 +13003,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5635157730802396</v>
+        <v>-0.564058618345835</v>
       </c>
       <c r="J9" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K9" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2563892281837522</v>
+        <v>0.258297629736213</v>
       </c>
       <c r="M9" t="n">
-        <v>5.923585171846223</v>
+        <v>5.903002737475089</v>
       </c>
       <c r="N9" t="n">
-        <v>59.72036152047747</v>
+        <v>59.48667204094273</v>
       </c>
       <c r="O9" t="n">
-        <v>7.727895025197836</v>
+        <v>7.712760338616955</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6675061311307</v>
+        <v>402.6728724733193</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -13016,7 +13062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J253"/>
+  <dimension ref="A1:J254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26171,6 +26217,58 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-35.171604770017254,173.0953901177291</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>-35.17191410082475,173.09620948499975</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>-35.17232058305882,173.09689658340642</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-35.1726593132766,173.0976431717294</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-35.17299349773342,173.09838792083886</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-35.17308784934261,173.09925063046018</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-35.17303937067412,173.10012716251777</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-35.172850900698336,173.10097652341227</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
